--- a/10_社畜アイコン/アイコン整理用.xlsx
+++ b/10_社畜アイコン/アイコン整理用.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\10_Cursor\40_社畜診断\10_社畜アイコン\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D745644A-833C-4A3A-BBDE-5F1C1ECB0C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AAE9302-5E4D-4C66-942C-56AECAE6048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{E20B84B2-3778-4FFC-AFDA-482A19C1B008}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="9960" xr2:uid="{E20B84B2-3778-4FFC-AFDA-482A19C1B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1019,19 +1020,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FB2812-4D4C-45CA-ADC1-7C8AB1AAC241}">
   <dimension ref="B2:E19"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="24.375" customWidth="1"/>
+    <col min="3" max="3" width="24.3984375" customWidth="1"/>
     <col min="4" max="4" width="9" style="4"/>
-    <col min="5" max="5" width="41.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1045,7 +1046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>2</v>
       </c>
@@ -1059,7 +1060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>3</v>
       </c>
@@ -1073,7 +1074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>4</v>
       </c>
@@ -1087,7 +1088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>5</v>
       </c>
@@ -1101,7 +1102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>6</v>
       </c>
@@ -1115,7 +1116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>7</v>
       </c>
@@ -1129,7 +1130,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>8</v>
       </c>
@@ -1143,7 +1144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>9</v>
       </c>
@@ -1157,7 +1158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>10</v>
       </c>
@@ -1171,7 +1172,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>11</v>
       </c>
@@ -1185,7 +1186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>12</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>13</v>
       </c>
@@ -1213,7 +1214,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>14</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>15</v>
       </c>
@@ -1241,7 +1242,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>16</v>
       </c>
@@ -1255,7 +1256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="2:5" ht="60" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
